--- a/Banking_Agent/reports/excel/698167220.xlsx
+++ b/Banking_Agent/reports/excel/698167220.xlsx
@@ -76,18 +76,18 @@
     <t>Intelligent Report</t>
   </si>
   <si>
-    <t>51,020 / Salary</t>
+    <t>110,346 / Neft</t>
   </si>
   <si>
     <t>Salary</t>
   </si>
   <si>
-    <t>Jan 2026: Jan 2026: ₹51,111 received (salary/employer credit) — ₹62,545 (122%) spent within 3 days (5 debits: ₹62,545 self-transfer) ₹51,111 | Ongoing (6 months): Ongoing (6 months): NACH mandate / SPLN EMI debit — avg ₹5,536/month (NACH-10-DR-PLA5150547202-3BPAN9NJ1HT2QB) ₹5,536 | Ongoing (2 months): Ongoing (2 months): EMI payment debit — avg ₹3,000/month (MB:SENT MONEY TO OWN 2411726562/EMI VEHICLE) ₹3,000 | Feb 2026: Feb 2026: ₹52,161 received (salary/employer credit) — ₹39,500 (76%) spent within 3 days (2 debits: ₹39,500 self-transfer) ₹52,161</t>
-  </si>
-  <si>
-    <t>The customer's banking profile presents a mixed picture. Their average monthly cash flow shows an inflow of ₹313,622 and outflow of ₹465,174, resulting in an average net deficit of ₹151,552 per month. This translates to a stretched obligation-to-income ratio of 51.8%, indicating that their income is barely covering their essential expenses.
-The customer's spending categories reveal some concerning trends. The largest portion of their expenditure goes towards self-transfers (420,345 INR), followed by finance and peer-to-peer transactions (545 INR). This suggests a high level of financial risk-taking, with a significant proportion of their income being diverted towards non-essential expenses. Furthermore, the customer's EMI payments are visible, indicating that they have taken on debt to purchase a vehicle.
-The customer's merchant behavior is also noteworthy. The most frequent merchant is PATELKISHANKUMA, which accounts for 32 transactions and ₹412,800 in spending. Additionally, there are regular merchants such as Salary Oct 2025, BHOSALE RAJU TA, PLA5150547202, and LM00849846, among others. The customer's favourite debit merchants include PLA5150547202 and LM00849846, while their favourite credit merchant is Salary Oct 2025. Notably, the customer has received high amounts of salary income from employer credits, with one instance in Jan 2026 where ₹51,111 was received and spent within 3 days at a rate of 122%.</t>
+    <t>Mar 2025: Mar 2025: ₹200,000 received (CASH DEPOSIT BY - SELF - KALWAKURTHY) — ₹231,035 (116%) spent within 3 days (34 debits: ₹231,035 third-party (34 txn)) ₹200,000 | May 2025: May 2025: ₹159,587 received (NEFT CR-CITI0100000-TATA CONSULTANCY SER VICES LIM) — ₹179,215 (112%) spent within 3 days (49 debits: ₹179,215 third-party (49 txn)) ₹159,587 | Apr 2025: Apr 2025: ₹129,719 received (salary/employer credit) — ₹102,783 (79%) spent within 3 days (46 debits: ₹102,783 third-party (46 txn)) ₹129,719 | Ongoing (2 months): Ongoing (2 months): Life / term insurance premium — avg ₹32,764/month (UPI-LIC BILLDESK-LIC.BILLDESK@HDFCBANK-H DFC0MERUPI-10044989) ₹32,764</t>
+  </si>
+  <si>
+    <t>The customer's banking profile indicates a monthly cash flow of ₹13,663, with an average net inflow of ₹2,456,353 and outflow of ₹2,401,699. The salary income is ₹110,346 per month from Neft transactions, while EMI commitments average ₹64,386 per payment. The customer's banking FOIR ratio stands at 58.3%, indicating a stretched obligation-to-income ratio.
+The customer's merchant behavior reveals a high frequency of transactions with Upi Al Arabian Mandi And 8074382799 Ybl Hdfc0004380 901173482826 Payment From Ph One Ref 901173482826, which accounts for 192 transactions and ₹383,577. The regular merchants listed include Upi Pilli Padmalatha Bharatpe 90072150211 Fbpe Fdrl0001382 194313697577 Pay To B Haratpe Me Ref 194313697577, Upi Syed Vajeed Ali 9603194936 Ybl Sbin 0006222 742082870771 Payment From Phone Ref 742082870771, and Upi Saleema Begum 9603564237 Hdfcbank Hd Fc0004380 503749685251 Payable Ref 503749685251 INR 8,000. The favourite debit merchants are Upi Syed Vajeed Ali 9603194936 Ybl Sbin 0006222 742082870771 Payment From Phone Ref 742082870771 and Upi Rainbow Hospitals Rainbowhospitals 41361814 Hdfcbank Hdfc0000001 037754862292 Generating Dynamic Ref 37754862292.
+The customer has experienced several transaction events, including receiving ₹200,000 in March 2025, which was spent within 3 days at a rate of 116%. In May 2025, the customer received ₹159,587 and spent it within 3 days at a rate of 112%. Additionally, the customer has been making regular payments for life / term insurance premium through UPI-LIC BILLDESK-LIC.BILLDESK@HDFCBANK-H DFC0MERUPI-10044989.</t>
   </si>
   <si>
     <t>Primary</t>
